--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-protocols-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/embedded-protocols-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Khi có nhiễu điện từ bên ngoài tác động, nó sẽ tác động lên cả hai dây CAN_H và CAN_L cùng một lượng điện áp tương đương (nhiễu đồng pha - Common-mode noise). Phép trừ hiệu điện áp ở bộ thu sẽ tự động triệt tiêu lượng nhiễu này, giúp tín hiệu CAN cực kỳ ổn định.</v>
       </c>
       <c r="F2" t="str">
-        <v>Sử dụng truyền truyền tín hiệu vi sai (Differential Signaling) qua cặp dây xoắn CAN_H và CAN_L; bộ thu đọc hiệu điện áp chênh lệch ($V_{diff} = V_{CAN_H} - V_{CAN_L}$) giúp triệt tiêu nhiễu đồng pha — truyền tín hiệu vi sai triệt tiêu nhiễu đồng pha</v>
+        <v>Được bọc một lớp vỏ bằng lá chì dày 5cm xung quanh toàn bộ đường dây dẫn — bọc lá chì bảo vệ</v>
       </c>
       <c r="G2" t="str">
         <v>Sử dụng cáp quang bằng thủy tinh để truyền dữ liệu bằng ánh sáng thay vì dòng điện — truyền bằng cáp quang</v>
       </c>
       <c r="H2" t="str">
-        <v>Được bọc một lớp vỏ bằng lá chì dày 5cm xung quanh toàn bộ đường dây dẫn — bọc lá chì bảo vệ</v>
+        <v>Tự động tăng điện áp truyền dẫn lên mức 1000V để vượt qua các nguồn nhiễu — tăng điện áp cực đoan</v>
       </c>
       <c r="I2" t="str">
-        <v>Tự động tăng điện áp truyền dẫn lên mức 1000V để vượt qua các nguồn nhiễu — tăng điện áp cực đoan</v>
+        <v>Sử dụng truyền truyền tín hiệu vi sai (Differential Signaling) qua cặp dây xoắn CAN_H và CAN_L; bộ thu đọc hiệu điện áp chênh lệch ($V_{diff} = V_{CAN_H} - V_{CAN_L}$) giúp triệt tiêu nhiễu đồng pha — truyền tín hiệu vi sai triệt tiêu nhiễu đồng pha</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>CPOL định nghĩa trạng thái của đường clock khi rảnh (Idle state); CPHA định nghĩa sườn xung clock (sườn lên hay sườn xuống) dùng để chốt mẫu dữ liệu (sample data) — cực tính và pha của xung nhịp clock</v>
       </c>
       <c r="G3" t="str">
+        <v>CPOL bắt buộc phải bằng 1 và CPHA bắt buộc phải bằng 0 trong mọi trường hợp kết nối — giá trị cấu hình cố định</v>
+      </c>
+      <c r="H3" t="str">
         <v>CPOL định nghĩa độ dài của bit dữ liệu truyền; CPHA định nghĩa tốc độ Baudrate của xung nhịp — độ dài bit và tốc độ</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>CPOL dùng để chọn chip Master; CPHA dùng để chọn chip Slave trong hệ thống — phân vai trò thiết bị</v>
-      </c>
-      <c r="I3" t="str">
-        <v>CPOL bắt buộc phải bằng 1 và CPHA bắt buộc phải bằng 0 trong mọi trường hợp kết nối — giá trị cấu hình cố định</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -530,10 +530,10 @@
         <v>Nút nào phát hiện va chạm sẽ tự động tăng công suất phát sóng để đè bẹp các tín hiệu của nút đối thủ — tăng công suất phát sóng</v>
       </c>
       <c r="H4" t="str">
+        <v>Master sẽ gửi lệnh ngắt ngẫu nhiên để chọn ra một nút ngẫu nhiên được quyền truyền tiếp — Master điều phối ngẫu nhiên</v>
+      </c>
+      <c r="I4" t="str">
         <v>Tất cả các nút đang truyền sẽ dừng lại, hệ thống tự động reset lại nguồn của xe ô tô — reset nguồn xe</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Master sẽ gửi lệnh ngắt ngẫu nhiên để chọn ra một nút ngẫu nhiên được quyền truyền tiếp — Master điều phối ngẫu nhiên</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -556,19 +556,19 @@
         <v>Mức TTL (0-3.3V) có biên nhiễu rất nhỏ, chạy dây dài sẽ bị nhiễu làm sai bit dữ liệu. RS232 sử dụng điện áp âm/dương lớn (+/- 3V đến +/- 15V) giúp đi xa hơn (15m). RS485 sử dụng vi sai (A-B) giúp đi cực xa (lên tới 1200m) trong môi trường công nghiệp nhiễu nặng.</v>
       </c>
       <c r="F5" t="str">
-        <v>Vì mức tín hiệu TTL (0-3.3V/5V) dễ bị suy hao và nhiễu trên đường dây dài; giải pháp là sử dụng chip chuyển đổi sang chuẩn RS232 (mức điện áp cao +/-15V) hoặc RS485 (tín hiệu vi sai) — chuyển đổi sang chuẩn RS232 hoặc RS485 chống nhiễu khoảng cách xa</v>
+        <v>Vì dây dẫn dài sẽ làm tăng điện trở và làm cháy cổng UART của vi điều khiển — cháy cổng UART do điện trở</v>
       </c>
       <c r="G5" t="str">
-        <v>Vì dây dẫn dài sẽ làm tăng điện trở và làm cháy cổng UART của vi điều khiển — cháy cổng UART do điện trở</v>
+        <v>Yêu cầu vi điều khiển phải chạy bằng pin 12V thay vì nguồn USB 5V — thay đổi nguồn điện chip</v>
       </c>
       <c r="H5" t="str">
         <v>Giải pháp là tăng tốc độ Baudrate lên mức tối đa để dữ liệu đi nhanh hơn tránh bị nhiễu dọc đường — tăng baudrate sai phương pháp</v>
       </c>
       <c r="I5" t="str">
-        <v>Yêu cầu vi điều khiển phải chạy bằng pin 12V thay vì nguồn USB 5V — thay đổi nguồn điện chip</v>
+        <v>Vì mức tín hiệu TTL (0-3.3V/5V) dễ bị suy hao và nhiễu trên đường dây dài; giải pháp là sử dụng chip chuyển đổi sang chuẩn RS232 (mức điện áp cao +/-15V) hoặc RS485 (tín hiệu vi sai) — chuyển đổi sang chuẩn RS232 hoặc RS485 chống nhiễu khoảng cách xa</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Đây là quy định vật lý của I2C. Khi bus rảnh, cả SDA và SCL đều ở mức High (nhờ điện trở pull-up). Khi bắt đầu truyền, Master tạo ra START condition. Quy tắc: Dữ liệu trên dây SDA chỉ được phép thay đổi khi SCL đang ở mức Low, và phải giữ nguyên khi SCL ở mức High, ngoại trừ điều kiện START và STOP.</v>
       </c>
       <c r="F6" t="str">
+        <v>START: Master kéo chân CS của Slave xuống đất; STOP: Master kéo chân CS lên mức cao — cơ chế CS của SPI</v>
+      </c>
+      <c r="G6" t="str">
+        <v>START: Gửi ký tự byte `0x02` (STX); STOP: Gửi ký tự byte `0x03` (ETX) — ký tự điều khiển ASCII</v>
+      </c>
+      <c r="H6" t="str">
+        <v>START: Trực tiếp cấp nguồn điện cho đường bus; STOP: Tắt nguồn điện của vi điều khiển — cấp ngắt nguồn điện</v>
+      </c>
+      <c r="I6" t="str">
         <v>START: SDA chuyển từ High sang Low khi SCL đang ở mức High; STOP: SDA chuyển từ Low sang High khi SCL đang ở mức High — START/STOP conditions của bus I2C</v>
       </c>
-      <c r="G6" t="str">
-        <v>START: Trực tiếp cấp nguồn điện cho đường bus; STOP: Tắt nguồn điện của vi điều khiển — cấp ngắt nguồn điện</v>
-      </c>
-      <c r="H6" t="str">
-        <v>START: Master kéo chân CS của Slave xuống đất; STOP: Master kéo chân CS lên mức cao — cơ chế CS của SPI</v>
-      </c>
-      <c r="I6" t="str">
-        <v>START: Gửi ký tự byte `0x02` (STX); STOP: Gửi ký tự byte `0x03` (ETX) — ký tự điều khiển ASCII</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>Xung điện truyền trên đường bus khi gặp điểm cuối dây (mở mạch) sẽ bị dội ngược lại (phản xạ), va chạm với các xung tiếp theo gây méo mó dạng sóng. Hai điện trở 120 Ohm mắc song song tạo ra trở kháng tương đương 60 Ohm khớp với trở kháng đặc tính của cáp CAN, hấp thụ hoàn toàn năng lượng sóng dội ngược.</v>
       </c>
       <c r="F7" t="str">
-        <v>Để triệt tiêu hiện tượng phản xạ tín hiệu (Signal Reflection) trên đường dây truyền dẫn dài, tránh làm biến dạng xung tín hiệu gây lỗi bit — triệt tiêu phản xạ tín hiệu</v>
+        <v>Để tăng tốc độ truyền dữ liệu của bus CAN lên mức tối đa 100 Mbps — tăng tốc độ bus CAN</v>
       </c>
       <c r="G7" t="str">
         <v>Để hạn chế dòng điện chạy qua dây dẫn tránh gây chập cháy hộp đen xe hơi — hạn chế dòng điện</v>
       </c>
       <c r="H7" t="str">
-        <v>Để tăng tốc độ truyền dữ liệu của bus CAN lên mức tối đa 100 Mbps — tăng tốc độ bus CAN</v>
+        <v>Để lọc các tần số nhiễu sinh ra từ bugi đánh lửa của động cơ xe ô tô — lọc nhiễu bugi</v>
       </c>
       <c r="I7" t="str">
-        <v>Để lọc các tần số nhiễu sinh ra từ bugi đánh lửa của động cơ xe ô tô — lọc nhiễu bugi</v>
+        <v>Để triệt tiêu hiện tượng phản xạ tín hiệu (Signal Reflection) trên đường dây truyền dẫn dài, tránh làm biến dạng xung tín hiệu gây lỗi bit — triệt tiêu phản xạ tín hiệu</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -655,10 +655,10 @@
         <v>Dùng để phát hiện lỗi bit đơn bằng cách đếm số lượng bit 1 là chẵn (Even) hay lẻ (Odd); giới hạn là không thể phát hiện lỗi nếu bị sai lệch đồng thời 2 bit — phát hiện lỗi bit đơn và giới hạn lỗi kép</v>
       </c>
       <c r="G8" t="str">
+        <v>Dùng để định vị địa chỉ của chip Slave nhận dữ liệu tiếp theo — định địa chỉ thiết bị</v>
+      </c>
+      <c r="H8" t="str">
         <v>Dùng để mã hóa bảo mật dữ liệu trước khi gửi lên đường truyền mạng — mã hóa dữ liệu</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Dùng để định vị địa chỉ của chip Slave nhận dữ liệu tiếp theo — định địa chỉ thiết bị</v>
       </c>
       <c r="I8" t="str">
         <v>Dùng để chỉ định sườn xung clock bắt đầu đọc dữ liệu mẫu — sườn xung clock</v>
@@ -684,19 +684,19 @@
         <v>I2C sử dụng cơ chế Wired-AND (nối cổng AND vật lý qua điện trở kéo lên). Master khi truyền luôn luôn lắng nghe trạng thái thực tế của đường bus SDA. Nếu nó gửi bit 1 (High) nhưng đọc thấy bus là 0 (Low - do Master kia kéo xuống), nó hiểu là đã thua cuộc trong quá trình Arbitration và lập tức rút lui nhường bus cho Master thắng cuộc.</v>
       </c>
       <c r="F9" t="str">
-        <v>Sử dụng cơ chế phân định bus (Bus Arbitration): Master nào đọc thấy đường SDA bị kéo xuống Low (bởi Master kia) trong khi nó muốn gửi High sẽ tự động dừng truyền và chuyển sang chế độ chờ — phân định bus dựa trên giám sát SDA</v>
+        <v>Hệ thống tự động kích hoạt ngắt reset nguồn của toàn bộ vi điều khiển trên mạch — reset nguồn</v>
       </c>
       <c r="G9" t="str">
         <v>Master nào có kích thước vật lý lớn hơn sẽ được ưu tiên chiếm quyền truyền trước — kích thước vật lý</v>
       </c>
       <c r="H9" t="str">
+        <v>Sử dụng cơ chế phân định bus (Bus Arbitration): Master nào đọc thấy đường SDA bị kéo xuống Low (bởi Master kia) trong khi nó muốn gửi High sẽ tự động dừng truyền và chuyển sang chế độ chờ — phân định bus dựa trên giám sát SDA</v>
+      </c>
+      <c r="I9" t="str">
         <v>Cả hai Master sẽ cùng truyền chèn đè tín hiệu lên nhau cho đến khi một trong hai bị hỏng chip — chèn đè tín hiệu</v>
       </c>
-      <c r="I9" t="str">
-        <v>Hệ thống tự động kích hoạt ngắt reset nguồn của toàn bộ vi điều khiển trên mạch — reset nguồn</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Tiết kiệm tối đa số lượng chân GPIO của Master vì tất cả các Slave dùng chung duy nhất một chân CS/SS chung — tiết kiệm chân GPIO Master nối tầng</v>
       </c>
       <c r="G10" t="str">
-        <v>Tốc độ truyền dữ liệu nhanh gấp 10 lần so với cách nối độc lập hình sao — tốc độ truyền tải</v>
+        <v>Hoàn toàn loại bỏ nhu cầu sử dụng dây xung nhịp SCK dùng chung — không dùng dây clock</v>
       </c>
       <c r="H10" t="str">
         <v>Mỗi Slave có thể tự đặt địa chỉ phần mềm độc lập giống giao thức I2C — định địa chỉ phần mềm</v>
       </c>
       <c r="I10" t="str">
-        <v>Hoàn toàn loại bỏ nhu cầu sử dụng dây xung nhịp SCK dùng chung — không dùng dây clock</v>
+        <v>Tốc độ truyền dữ liệu nhanh gấp 10 lần so với cách nối độc lập hình sao — tốc độ truyền tải</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>I2C Master điều phối xung nhịp SCL. Tuy nhiên, nếu Slave bị quá tải (đang bận xử lý ngắt, chưa đọc kịp byte cũ từ buffer), nó có thể giữ đường SCL xuống đất (Low). Master đọc thấy SCL vẫn Low sẽ không phát xung tiếp theo mà dừng lại đợi cho đến khi Slave thả SCL lên High mới truyền tiếp.</v>
       </c>
       <c r="F11" t="str">
-        <v>Do Slave thực hiện bằng cách kéo và giữ đường SCL xuống mức Low để bắt Master phải dừng truyền, chờ Slave xử lý xong dữ liệu — Slave kéo giữ SCL trì hoãn Master</v>
+        <v>Do Master thực hiện để tăng tốc độ truyền nhận dữ liệu của bus lên nhanh gấp đôi — tăng tốc độ bus</v>
       </c>
       <c r="G11" t="str">
-        <v>Do Master thực hiện để tăng tốc độ truyền nhận dữ liệu của bus lên nhanh gấp đôi — tăng tốc độ bus</v>
+        <v>Là hành động lập trình viên viết code cấu hình lại tần số thạch anh ngoại vi của chip — cấu hình thạch anh</v>
       </c>
       <c r="H11" t="str">
         <v>Do điện trở kéo lên tự động thực hiện khi nhiệt độ môi trường tăng lên quá cao — tác động nhiệt điện trở</v>
       </c>
       <c r="I11" t="str">
-        <v>Là hành động lập trình viên viết code cấu hình lại tần số thạch anh ngoại vi của chip — cấu hình thạch anh</v>
+        <v>Do Slave thực hiện bằng cách kéo và giữ đường SCL xuống mức Low để bắt Master phải dừng truyền, chờ Slave xử lý xong dữ liệu — Slave kéo giữ SCL trì hoãn Master</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
